--- a/Development/Common/GameData/SpawnGroup.xlsx
+++ b/Development/Common/GameData/SpawnGroup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnGroup" sheetId="1" state="visible" r:id="rId1"/>
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="21.25" customWidth="1" style="12" min="1" max="1"/>
@@ -571,7 +571,8 @@
     <col width="19.25" customWidth="1" style="3" min="9" max="9"/>
     <col width="18.75" customWidth="1" style="3" min="10" max="10"/>
     <col width="19.75" customWidth="1" style="3" min="11" max="11"/>
-    <col width="9" customWidth="1" style="3" min="12" max="16384"/>
+    <col width="9" customWidth="1" style="3" min="12" max="12"/>
+    <col width="9" customWidth="1" style="3" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1097,13 +1098,13 @@
         <v>59</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>5</v>
@@ -1124,25 +1125,61 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>52</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
         <v>53</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RaidBoss</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>레이드1 보스: 찬탈자 드래곤 단독</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>70</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
